--- a/5_cobranza/inputs/pagos_yape/pagos_yape_tepago.xlsx
+++ b/5_cobranza/inputs/pagos_yape/pagos_yape_tepago.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,7 +92,17 @@
     </font>
     <font>
       <name val="Courier New"/>
+      <color rgb="007D6608"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
       <color rgb="007C3003"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="000C447C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -102,22 +112,7 @@
     </font>
     <font>
       <name val="Courier New"/>
-      <color rgb="000C447C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
       <color rgb="001D4ED8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="00A32D2D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Courier New"/>
-      <color rgb="007D6608"/>
       <sz val="10"/>
     </font>
     <font>
@@ -132,7 +127,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -197,11 +192,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EFF6FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCEBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -303,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -363,33 +353,30 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -757,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -790,43 +777,43 @@
           <t>¿QUIÉN ES?</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="28" t="n"/>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="27" t="n"/>
       <c r="D1" s="2" t="inlineStr"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
           <t>¿QUÉ HIZO EL BANCO?</t>
         </is>
       </c>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="28" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="27" t="n"/>
       <c r="L1" s="2" t="inlineStr"/>
       <c r="M1" s="4" t="inlineStr">
         <is>
           <t>¿DÓNDE VIVE?</t>
         </is>
       </c>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="28" t="n"/>
+      <c r="N1" s="26" t="n"/>
+      <c r="O1" s="27" t="n"/>
       <c r="P1" s="2" t="inlineStr"/>
       <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>¿CUÁNTO DEBE?</t>
         </is>
       </c>
-      <c r="R1" s="27" t="n"/>
-      <c r="S1" s="28" t="n"/>
+      <c r="R1" s="26" t="n"/>
+      <c r="S1" s="27" t="n"/>
       <c r="T1" s="2" t="inlineStr"/>
       <c r="U1" s="6" t="inlineStr">
         <is>
           <t>¿CUÁNDO?</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="28" t="inlineStr">
         <is>
           <t>¿CUÁNDO?</t>
         </is>
@@ -922,7 +909,7 @@
           <t>CICLO</t>
         </is>
       </c>
-      <c r="V2" s="30" t="inlineStr">
+      <c r="V2" s="29" t="inlineStr">
         <is>
           <t>CICLO_COBRANZA</t>
         </is>
@@ -984,22 +971,22 @@
       <c r="O3" s="19" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="20" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R3" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S3" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" s="31" t="n">
-        <v>2</v>
+      <c r="U3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1058,22 +1045,22 @@
       <c r="O4" s="19" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R4" s="20" t="n">
-        <v>92</v>
-      </c>
-      <c r="S4" s="22" t="inlineStr">
-        <is>
-          <t>exceso</t>
+        <v>0</v>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" s="31" t="n">
-        <v>2</v>
+      <c r="U4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1132,28 +1119,28 @@
       <c r="O5" s="19" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S5" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="31" t="n">
-        <v>2</v>
+      <c r="U5" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="12" t="inlineStr"/>
       <c r="B6" s="13" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>blanco</t>
         </is>
@@ -1199,13 +1186,13 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="20" t="inlineStr"/>
       <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="24" t="inlineStr">
+      <c r="S6" s="25" t="inlineStr">
         <is>
           <t>concepto</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="21" t="n">
+      <c r="U6" s="22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1265,22 +1252,22 @@
       <c r="O7" s="19" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="20" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S7" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="31" t="n">
-        <v>2</v>
+      <c r="U7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1339,22 +1326,22 @@
       <c r="O8" s="19" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="20" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="R8" s="20" t="n">
-        <v>-100</v>
-      </c>
-      <c r="S8" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S8" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="31" t="n">
-        <v>2</v>
+      <c r="U8" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1413,22 +1400,22 @@
       <c r="O9" s="19" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="20" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S9" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="31" t="n">
-        <v>2</v>
+      <c r="U9" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1487,22 +1474,22 @@
       <c r="O10" s="19" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S10" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="31" t="n">
-        <v>2</v>
+      <c r="U10" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1561,22 +1548,22 @@
       <c r="O11" s="19" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="20" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="R11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S11" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="31" t="n">
-        <v>2</v>
+      <c r="U11" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1635,22 +1622,22 @@
       <c r="O12" s="19" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="20" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="R12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S12" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr"/>
-      <c r="U12" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" s="31" t="n">
-        <v>2</v>
+      <c r="U12" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1709,22 +1696,22 @@
       <c r="O13" s="19" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="R13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S13" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr"/>
-      <c r="U13" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" s="31" t="n">
-        <v>2</v>
+      <c r="U13" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1783,19 +1770,22 @@
       <c r="O14" s="19" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="20" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="R14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr"/>
-      <c r="U14" s="21" t="n">
-        <v>2</v>
+      <c r="U14" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1809,7 +1799,7 @@
           <t>GREGORIO TOLENTINO SANCHEZ</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>correccion</t>
         </is>
@@ -1854,22 +1844,22 @@
       <c r="O15" s="19" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R15" s="20" t="n">
-        <v>-75</v>
-      </c>
-      <c r="S15" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr"/>
-      <c r="U15" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="31" t="n">
-        <v>2</v>
+      <c r="U15" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1928,27 +1918,38 @@
       <c r="O16" s="19" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="20" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="R16" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr"/>
-      <c r="U16" s="21" t="n">
-        <v>2</v>
+      <c r="U16" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr"/>
-      <c r="B17" s="13" t="inlineStr"/>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>U0469</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>JULIO VEGA CERDA</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1959,51 +1960,70 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Julio Veg*</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr"/>
       <c r="H17" s="16" t="n">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="I17" s="16" t="inlineStr"/>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>geral cobro de agua</t>
+          <t xml:space="preserve">Mz E1 Lte 8. de faenas están canceladas. por lo que no </t>
         </is>
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>07/06/2026 10:39:56</t>
+          <t>07/06/2026 10:08:59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="18" t="inlineStr"/>
-      <c r="N17" s="18" t="inlineStr"/>
-      <c r="O17" s="19" t="inlineStr">
-        <is>
-          <t>cobro de agua (Yerald)</t>
-        </is>
-      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O17" s="19" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="20" t="inlineStr"/>
-      <c r="R17" s="20" t="inlineStr"/>
-      <c r="S17" s="24" t="inlineStr">
-        <is>
-          <t>concepto</t>
+      <c r="Q17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="21" t="n">
-        <v>2</v>
+      <c r="U17" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="12" t="inlineStr"/>
-      <c r="B18" s="13" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>U0464</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>JHONNY SALOMON NIÑO ORTIZ</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -2014,54 +2034,65 @@
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Janet Vil*</t>
+          <t>Renee Med*</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr"/>
       <c r="H18" s="16" t="n">
-        <v>450</v>
+        <v>8</v>
       </c>
       <c r="I18" s="16" t="inlineStr"/>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>350#1cobro 100 # cobro maximo</t>
+          <t xml:space="preserve">Johnny Salomón Niño Ortiz (Mz E1 lote 1) (exonerado </t>
         </is>
       </c>
       <c r="K18" s="15" t="inlineStr">
         <is>
-          <t>07/06/2026 10:39:01</t>
+          <t>07/06/2026 09:08:06</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="18" t="inlineStr"/>
-      <c r="N18" s="18" t="inlineStr"/>
-      <c r="O18" s="19" t="inlineStr">
-        <is>
-          <t>cobro de agua (Maximo)</t>
-        </is>
-      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="20" t="inlineStr"/>
-      <c r="R18" s="20" t="inlineStr"/>
-      <c r="S18" s="24" t="inlineStr">
-        <is>
-          <t>concepto</t>
+      <c r="Q18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="21" t="n">
-        <v>2</v>
+      <c r="U18" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>U0469</t>
+          <t>U0426</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>JULIO VEGA CERDA</t>
+          <t>ALBERTO CHINCHAY PARIAMACHI</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -2077,7 +2108,7 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Julio Veg*</t>
+          <t>Sandra Del*</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr"/>
@@ -2087,52 +2118,55 @@
       <c r="I19" s="16" t="inlineStr"/>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mz E1 Lte 8. de faenas están canceladas. por lo que no </t>
+          <t xml:space="preserve">mza.A1 lote 4 Alberto chinchay pariamachi  </t>
         </is>
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>07/06/2026 10:08:59</t>
+          <t>07/06/2026 08:27:29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="N19" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O19" s="19" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R19" s="20" t="n">
-        <v>-31</v>
-      </c>
-      <c r="S19" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S19" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="21" t="n">
-        <v>2</v>
+      <c r="U19" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>U0464</t>
+          <t>U0264</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>JHONNY SALOMON NIÑO ORTIZ</t>
+          <t>EDGAR MELGAREJO BEDON</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2148,7 +2182,7 @@
       </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>Renee Med*</t>
+          <t>Edgar Mel*</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr"/>
@@ -2158,57 +2192,60 @@
       <c r="I20" s="16" t="inlineStr"/>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johnny Salomón Niño Ortiz (Mz E1 lote 1) (exonerado </t>
+          <t>mz o lt 16 Edgar melgarejo</t>
         </is>
       </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>07/06/2026 09:08:06</t>
+          <t>06/06/2026 22:48:23</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="N20" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O20" s="19" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="20" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R20" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S20" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S20" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr"/>
-      <c r="U20" s="21" t="n">
-        <v>2</v>
+      <c r="U20" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>U0426</t>
+          <t>U0010</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>ALBERTO CHINCHAY PARIAMACHI</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ALEJANDRO MELGAREJO ESPINOZA</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -2219,62 +2256,65 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Sandra Del*</t>
+          <t>Jose Mel*</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
       <c r="H21" s="16" t="n">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="I21" s="16" t="inlineStr"/>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">mza.A1 lote 4 Alberto chinchay pariamachi  </t>
+          <t xml:space="preserve">pago del servicio de agua, usuario Alejandro Melgarejo, </t>
         </is>
       </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>07/06/2026 08:27:29</t>
+          <t>06/06/2026 21:59:44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N21" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O21" s="19" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S21" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="21" t="n">
-        <v>2</v>
+      <c r="U21" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>U0264</t>
+          <t>U0288</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>EDGAR MELGAREJO BEDON</t>
+          <t>JUDITH VENTURO ROSALES</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2290,67 +2330,70 @@
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Edgar Mel*</t>
+          <t>Judith Ven*</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr"/>
       <c r="H22" s="16" t="n">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="I22" s="16" t="inlineStr"/>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>mz o lt 16 Edgar melgarejo</t>
+          <t>manzana P lote 12</t>
         </is>
       </c>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 22:48:23</t>
+          <t>06/06/2026 21:46:01</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>P</t>
         </is>
       </c>
       <c r="N22" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O22" s="19" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R22" s="20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S22" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S22" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="21" t="n">
-        <v>2</v>
+      <c r="U22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>U0010</t>
+          <t>U0105</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>ALEJANDRO MELGAREJO ESPINOZA</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>TOLENTINO JULCA MORENO</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -2361,62 +2404,65 @@
       </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
-          <t>Jose Mel*</t>
+          <t>Elma Rom*</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr"/>
       <c r="H23" s="16" t="n">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="I23" s="16" t="inlineStr"/>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pago del servicio de agua, usuario Alejandro Melgarejo, </t>
+          <t>mz f lote 4 tolentino julca</t>
         </is>
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 21:59:44</t>
+          <t>06/06/2026 21:44:17</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="N23" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O23" s="19" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="20" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R23" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S23" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr"/>
-      <c r="U23" s="21" t="n">
-        <v>2</v>
+      <c r="U23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>U0288</t>
+          <t>U0039</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>JUDITH VENTURO ROSALES</t>
+          <t>JULISSA BARRETO QUITO</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2432,62 +2478,65 @@
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Judith Ven*</t>
+          <t>Julissa Bar*</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr"/>
       <c r="H24" s="16" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I24" s="16" t="inlineStr"/>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>manzana P lote 12</t>
+          <t>Mz C LT 8</t>
         </is>
       </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 21:46:01</t>
+          <t>06/06/2026 21:26:17</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N24" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="19" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="20" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S24" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr"/>
-      <c r="U24" s="21" t="n">
-        <v>2</v>
+      <c r="U24" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>U0105</t>
+          <t>U0166</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>TOLENTINO JULCA MORENO</t>
+          <t>EUGENIO LEONCIO MOYA DURAND</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -2503,28 +2552,28 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Elma Rom*</t>
+          <t>Llitech Moy*</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr"/>
       <c r="H25" s="16" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I25" s="16" t="inlineStr"/>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>mz f lote 4 tolentino julca</t>
+          <t>Mz: i - Lt: 4</t>
         </is>
       </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 21:44:17</t>
+          <t>06/06/2026 20:46:49</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N25" s="18" t="inlineStr">
@@ -2535,30 +2584,29 @@
       <c r="O25" s="19" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="20" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="R25" s="20" t="n">
-        <v>-125</v>
-      </c>
-      <c r="S25" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S25" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="21" t="n">
-        <v>2</v>
+      <c r="U25" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>U0039</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>JULISSA BARRETO QUITO</t>
+          <t>SAORY RAPRAY SILVA</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2574,67 +2622,70 @@
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Julissa Bar*</t>
+          <t>Melissa Pil*</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr"/>
       <c r="H26" s="16" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="I26" s="16" t="inlineStr"/>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>Mz C LT 8</t>
+          <t>Melissa MZB Lt 15</t>
         </is>
       </c>
       <c r="K26" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 21:26:17</t>
+          <t>06/06/2026 19:19:54</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N26" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O26" s="19" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="20" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="R26" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S26" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="21" t="n">
-        <v>2</v>
+      <c r="U26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>U0166</t>
+          <t>U0446</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>EUGENIO LEONCIO MOYA DURAND</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>AUBERTINA TRUJILLO TOLENTINO</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -2645,63 +2696,70 @@
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Llitech Moy*</t>
+          <t>PLIN - WILLIAM MANUEL CUADROS CERREPE</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr"/>
       <c r="H27" s="16" t="n">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="I27" s="16" t="inlineStr"/>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>Mz: i - Lt: 4</t>
+          <t>Aubertina Trujillo T</t>
         </is>
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 20:46:49</t>
+          <t>06/06/2026 18:48:11</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N27" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O27" s="19" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R27" s="20" t="n">
-        <v>-20</v>
-      </c>
-      <c r="S27" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S27" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr"/>
-      <c r="U27" s="21" t="n">
-        <v>2</v>
+      <c r="U27" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="12" t="inlineStr"/>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>U0393</t>
+        </is>
+      </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>SAORY RAPRAY SILVA</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>FELIPE JESUS ORTIZ APONTE</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -2712,67 +2770,70 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Melissa Pil*</t>
+          <t>Felipe Ort*</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
       <c r="H28" s="16" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="I28" s="16" t="inlineStr"/>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Melissa MZB Lt 15</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K28" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 19:19:54</t>
+          <t>06/06/2026 17:49:18</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N28" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O28" s="19" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="20" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="R28" s="20" t="n">
-        <v>-55</v>
-      </c>
-      <c r="S28" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S28" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="21" t="n">
-        <v>2</v>
+      <c r="U28" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>U0446</t>
+          <t>U0097</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>AUBERTINA TRUJILLO TOLENTINO</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>TEOFILA FERNANDEZ REYES</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -2783,67 +2844,70 @@
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>PLIN - WILLIAM MANUEL CUADROS CERREPE</t>
+          <t>Grabiela Val*</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr"/>
       <c r="H29" s="16" t="n">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="I29" s="16" t="inlineStr"/>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>Aubertina Trujillo T</t>
+          <t xml:space="preserve">TEOFILA FERNANDEZ REYES MZ E Lt12 la loza se va </t>
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 18:48:11</t>
+          <t>06/06/2026 17:23:01</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E</t>
         </is>
       </c>
       <c r="N29" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O29" s="19" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="20" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S29" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="21" t="n">
-        <v>2</v>
+      <c r="U29" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>U0393</t>
+          <t>U0372</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>FELIPE JESUS ORTIZ APONTE</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>RENATO ALBORNOS SIGUEÑAS</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -2854,67 +2918,70 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Felipe Ort*</t>
+          <t>Marisol Rom*</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
       <c r="H30" s="16" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I30" s="16" t="inlineStr"/>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mzn.W.Lt.5</t>
         </is>
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 17:49:18</t>
+          <t>06/06/2026 16:53:38</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>W</t>
         </is>
       </c>
       <c r="N30" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O30" s="19" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S30" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="21" t="n">
-        <v>2</v>
+      <c r="U30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>U0097</t>
+          <t>U0434</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>TEOFILA FERNANDEZ REYES</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>JOHAN ENSO RODRIGUEZ FLORES</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -2925,62 +2992,65 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Grabiela Val*</t>
+          <t>Johan Rod*</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr"/>
       <c r="H31" s="16" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="I31" s="16" t="inlineStr"/>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEOFILA FERNANDEZ REYES MZ E Lt12 la loza se va </t>
+          <t>MZ, B1.Lt..3=Johan Rodriguez Flores</t>
         </is>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 17:23:01</t>
+          <t>06/06/2026 16:35:56</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="N31" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O31" s="19" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="20" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="R31" s="20" t="n">
-        <v>-51</v>
-      </c>
-      <c r="S31" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S31" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="21" t="n">
-        <v>2</v>
+      <c r="U31" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>U0372</t>
+          <t>U0187</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>RENATO ALBORNOS SIGUEÑAS</t>
+          <t>HAYDEE RIMAC ALBERTO</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2996,67 +3066,70 @@
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>Marisol Rom*</t>
+          <t>Alberto Lop*</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
       <c r="H32" s="16" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="I32" s="16" t="inlineStr"/>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>Mzn.W.Lt.5</t>
+          <t>Haydee Rimac Alberto.    Mz J.    Lt. 7</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 16:53:38</t>
+          <t>06/06/2026 16:33:15</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N32" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O32" s="19" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R32" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S32" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S32" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr"/>
-      <c r="U32" s="21" t="n">
-        <v>2</v>
+      <c r="U32" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>U0434</t>
+          <t>U0064</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>JOHAN ENSO RODRIGUEZ FLORES</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>EBER AGÜERO TRUJILLO</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -3067,62 +3140,65 @@
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Johan Rod*</t>
+          <t>Eber Agu*</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
       <c r="H33" s="16" t="n">
-        <v>108</v>
+        <v>8</v>
       </c>
       <c r="I33" s="16" t="inlineStr"/>
       <c r="J33" s="17" t="inlineStr">
         <is>
-          <t>MZ, B1.Lt..3=Johan Rodriguez Flores</t>
+          <t>MZ. C LTE. 34 Faena exonerado</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 16:35:56</t>
+          <t>06/06/2026 14:00:31</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N33" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="O33" s="19" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S33" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr"/>
-      <c r="U33" s="21" t="n">
-        <v>2</v>
+      <c r="U33" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V33" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>U0187</t>
+          <t>U0059</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>HAYDEE RIMAC ALBERTO</t>
+          <t>OSTIN AGÜERO TRUJILLO</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3138,62 +3214,65 @@
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Alberto Lop*</t>
+          <t>Eber Agu*</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr"/>
       <c r="H34" s="16" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I34" s="16" t="inlineStr"/>
       <c r="J34" s="17" t="inlineStr">
         <is>
-          <t>Haydee Rimac Alberto.    Mz J.    Lt. 7</t>
+          <t>MZ. C LTE. 28</t>
         </is>
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 16:33:15</t>
+          <t>06/06/2026 13:59:09</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N34" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O34" s="19" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="20" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="R34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S34" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr"/>
-      <c r="U34" s="21" t="n">
-        <v>2</v>
+      <c r="U34" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>U0064</t>
+          <t>U0038</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>EBER AGÜERO TRUJILLO</t>
+          <t>VICTOR LOPEZ TRUJILLO</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
@@ -3209,22 +3288,22 @@
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Eber Agu*</t>
+          <t>Katherine Vil*</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr"/>
       <c r="H35" s="16" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="I35" s="16" t="inlineStr"/>
       <c r="J35" s="17" t="inlineStr">
         <is>
-          <t>MZ. C LTE. 34 Faena exonerado</t>
+          <t>mz C lt 7</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 14:00:31</t>
+          <t>06/06/2026 12:26:01</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
@@ -3235,36 +3314,39 @@
       </c>
       <c r="N35" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O35" s="19" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R35" s="20" t="n">
-        <v>-30</v>
-      </c>
-      <c r="S35" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S35" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr"/>
-      <c r="U35" s="21" t="n">
-        <v>2</v>
+      <c r="U35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>U0059</t>
+          <t>U0067</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>OSTIN AGÜERO TRUJILLO</t>
+          <t>RAQUEL SORIA BUSTAMANTE</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3280,22 +3362,22 @@
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Eber Agu*</t>
+          <t>Mery Bus*</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr"/>
       <c r="H36" s="16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I36" s="16" t="inlineStr"/>
       <c r="J36" s="17" t="inlineStr">
         <is>
-          <t>MZ. C LTE. 28</t>
+          <t>MZC    LT 37 ..raquel Valery Soria Bustamante</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 13:59:09</t>
+          <t>06/06/2026 12:14:12</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
@@ -3306,41 +3388,44 @@
       </c>
       <c r="N36" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O36" s="19" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="20" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="R36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S36" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="21" t="n">
-        <v>2</v>
+      <c r="U36" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>U0038</t>
+          <t>U0208</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>VICTOR LOPEZ TRUJILLO</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>MARCIAL SANCHEZ ARAOZ</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -3351,67 +3436,70 @@
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Katherine Vil*</t>
+          <t>PLIN - GIOVANNA VANESSA SANCHEZ MEZA</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr"/>
       <c r="H37" s="16" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="I37" s="16" t="inlineStr"/>
       <c r="J37" s="17" t="inlineStr">
         <is>
-          <t>mz C lt 7</t>
+          <t>Marcial Sánchez Aráoz Mk lt 17</t>
         </is>
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 12:26:01</t>
+          <t>05/06/2026 20:39:00</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="N37" s="18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O37" s="19" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="R37" s="20" t="n">
-        <v>-30</v>
-      </c>
-      <c r="S37" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S37" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="21" t="n">
-        <v>2</v>
+      <c r="U37" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V37" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>U0067</t>
+          <t>U0431</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>RAQUEL SORIA BUSTAMANTE</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>DIEGO LÓPEZ MUÑOZ</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -3422,67 +3510,70 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Mery Bus*</t>
+          <t>AGORA - DIEGO FABRICIO LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr"/>
       <c r="H38" s="16" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="I38" s="16" t="inlineStr"/>
       <c r="J38" s="17" t="inlineStr">
         <is>
-          <t>MZC    LT 37 ..raquel Valery Soria Bustamante</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>06/06/2026 12:14:12</t>
+          <t>05/06/2026 18:42:50</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="N38" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" s="19" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="20" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="R38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S38" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr"/>
-      <c r="U38" s="21" t="n">
-        <v>2</v>
+      <c r="U38" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V38" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>U0208</t>
+          <t>U0225</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>MARCIAL SANCHEZ ARAOZ</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>MERCURIO LUNA FLORES</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -3493,62 +3584,65 @@
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>PLIN - GIOVANNA VANESSA SANCHEZ MEZA</t>
+          <t>Jose Gre*</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr"/>
       <c r="H39" s="16" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="I39" s="16" t="inlineStr"/>
       <c r="J39" s="17" t="inlineStr">
         <is>
-          <t>Marcial Sánchez Aráoz Mk lt 17</t>
+          <t>usuario : mercurio luna flores mz.m Lt3</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 20:39:00</t>
+          <t>05/06/2026 18:11:18</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N39" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O39" s="19" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="20" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="R39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S39" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr"/>
-      <c r="U39" s="21" t="n">
-        <v>2</v>
+      <c r="U39" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V39" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>U0431</t>
+          <t>U0182</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>DIEGO LÓPEZ MUÑOZ</t>
+          <t>HECTOR AGÜERO TRUJILLO</t>
         </is>
       </c>
       <c r="C40" s="23" t="inlineStr">
@@ -3564,67 +3658,70 @@
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>AGORA - DIEGO FABRICIO LOPEZ MUNOZ</t>
+          <t>Hector Agu*</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr"/>
       <c r="H40" s="16" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="I40" s="16" t="inlineStr"/>
       <c r="J40" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mz..."J"    Lt..."2".</t>
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 18:42:50</t>
+          <t>05/06/2026 17:35:56</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="18" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N40" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O40" s="19" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="20" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S40" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="21" t="n">
-        <v>2</v>
+      <c r="U40" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>U0225</t>
+          <t>U0065</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>MERCURIO LUNA FLORES</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ANALY QUINECHE MORANTE</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -3635,62 +3732,65 @@
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>Jose Gre*</t>
+          <t>PLIN - ANALI QUINECHE</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr"/>
       <c r="H41" s="16" t="n">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="I41" s="16" t="inlineStr"/>
       <c r="J41" s="17" t="inlineStr">
         <is>
-          <t>usuario : mercurio luna flores mz.m Lt3</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 18:11:18</t>
+          <t>05/06/2026 17:34:08</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N41" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O41" s="19" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="20" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S41" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="21" t="n">
-        <v>2</v>
+      <c r="U41" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>U0182</t>
+          <t>U0008</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>HECTOR AGÜERO TRUJILLO</t>
+          <t>VICTOR MELGAREJO CORCINO</t>
         </is>
       </c>
       <c r="C42" s="23" t="inlineStr">
@@ -3706,65 +3806,68 @@
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Hector Agu*</t>
+          <t>Jesus Mel*</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr"/>
       <c r="H42" s="16" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="I42" s="16" t="inlineStr"/>
       <c r="J42" s="17" t="inlineStr">
         <is>
-          <t>mz..."J"    Lt..."2".</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 17:35:56</t>
+          <t>05/06/2026 12:34:58</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N42" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O42" s="19" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S42" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr"/>
-      <c r="U42" s="21" t="n">
-        <v>2</v>
+      <c r="U42" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>U0065</t>
+          <t>U0183</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>ANALY QUINECHE MORANTE</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
+          <t>VILMA CELESTINO VILLAFANA</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>correccion</t>
         </is>
@@ -3777,12 +3880,12 @@
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>PLIN - ANALI QUINECHE</t>
+          <t>PLIN - Vilma Norma Celestino Villafana</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr"/>
       <c r="H43" s="16" t="n">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="I43" s="16" t="inlineStr"/>
       <c r="J43" s="17" t="inlineStr">
@@ -3792,55 +3895,55 @@
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 17:34:08</t>
+          <t>05/06/2026 11:58:03</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="N43" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O43" s="19" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="20" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R43" s="20" t="n">
-        <v>-375</v>
-      </c>
-      <c r="S43" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S43" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V43" s="31" t="n">
-        <v>2</v>
+      <c r="U43" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>U0008</t>
+          <t>U0017</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>VICTOR MELGAREJO CORCINO</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>POMPEYO CELESTINO LLIUYA</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -3851,12 +3954,12 @@
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Jesus Mel*</t>
+          <t>PLIN - Vilma Norma Celestino Villafana</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr"/>
       <c r="H44" s="16" t="n">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="I44" s="16" t="inlineStr"/>
       <c r="J44" s="17" t="inlineStr">
@@ -3866,52 +3969,55 @@
       </c>
       <c r="K44" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 12:34:58</t>
+          <t>05/06/2026 11:54:46</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N44" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O44" s="19" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="20" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S44" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="21" t="n">
-        <v>2</v>
+      <c r="U44" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V44" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>U0183</t>
+          <t>U0012</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>VILMA CELESTINO VILLAFANA</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>FELIX POZO CASTRO</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -3922,67 +4028,70 @@
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>PLIN - Vilma Norma Celestino Villafana</t>
+          <t>Felix Poz*</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr"/>
       <c r="H45" s="16" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I45" s="16" t="inlineStr"/>
       <c r="J45" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MZ ALT 11 felix pozo   revisar corte</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 11:58:03</t>
+          <t>05/06/2026 11:12:37</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="18" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N45" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O45" s="19" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S45" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="21" t="n">
-        <v>2</v>
+      <c r="U45" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V45" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>U0017</t>
+          <t>U0041</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>POMPEYO CELESTINO LLIUYA</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>JUAN UCULMANA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -3993,70 +4102,70 @@
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>PLIN - Vilma Norma Celestino Villafana</t>
+          <t>BCP - UCULMANA GOMEZ OLGA ESTHER</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr"/>
       <c r="H46" s="16" t="n">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="I46" s="16" t="inlineStr"/>
       <c r="J46" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pagos de gastos de agua y multas casa tupac</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 11:54:46</t>
+          <t>05/06/2026 03:13:22</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N46" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O46" s="19" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="20" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="R46" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S46" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S46" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V46" s="31" t="n">
-        <v>2</v>
+      <c r="U46" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V46" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>U0012</t>
+          <t>U0053</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>FELIX POZO CASTRO</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ABRAHAM BARRERA VEGA</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -4067,67 +4176,70 @@
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Felix Poz*</t>
+          <t>Francisco Acu*</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr"/>
       <c r="H47" s="16" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="I47" s="16" t="inlineStr"/>
       <c r="J47" s="17" t="inlineStr">
         <is>
-          <t>MZ ALT 11 felix pozo   revisar corte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 11:12:37</t>
+          <t>04/06/2026 15:37:58</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N47" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O47" s="19" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="20" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="R47" s="20" t="n">
-        <v>-40</v>
-      </c>
-      <c r="S47" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S47" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr"/>
-      <c r="U47" s="21" t="n">
-        <v>2</v>
+      <c r="U47" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V47" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>U0041</t>
+          <t>U0173</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>JUAN UCULMANA SANCHEZ</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>DOMINGA CHACARA LOPEZ</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -4138,67 +4250,70 @@
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>BCP - UCULMANA GOMEZ OLGA ESTHER</t>
+          <t>Juan Rio*</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr"/>
       <c r="H48" s="16" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="I48" s="16" t="inlineStr"/>
       <c r="J48" s="17" t="inlineStr">
         <is>
-          <t>Pagos de gastos de agua y multas casa tupac</t>
+          <t>Dominga chaccara López mz i lote 11</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>05/06/2026 03:13:22</t>
+          <t>03/06/2026 20:52:08</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N48" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O48" s="19" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="20" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="R48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S48" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr"/>
-      <c r="U48" s="21" t="n">
-        <v>2</v>
+      <c r="U48" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>U0053</t>
+          <t>U0405</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>ABRAHAM BARRERA VEGA</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>maestro</t>
+          <t>FELIX LUNA LOPEZ</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -4209,12 +4324,12 @@
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Francisco Acu*</t>
+          <t>Maria Alv*</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr"/>
       <c r="H49" s="16" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I49" s="16" t="inlineStr"/>
       <c r="J49" s="17" t="inlineStr">
@@ -4224,47 +4339,50 @@
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>04/06/2026 15:37:58</t>
+          <t>03/06/2026 19:50:28</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="N49" s="18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O49" s="19" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S49" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr"/>
-      <c r="U49" s="21" t="n">
-        <v>2</v>
+      <c r="U49" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V49" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>U0173</t>
+          <t>U0066</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>DOMINGA CHACARA LOPEZ</t>
+          <t>MARIA NORABUENA ESPADA</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4280,67 +4398,70 @@
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Juan Rio*</t>
+          <t>BCP - JACOME NORABUENA JESUS ELVIRO</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr"/>
       <c r="H50" s="16" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="I50" s="16" t="inlineStr"/>
       <c r="J50" s="17" t="inlineStr">
         <is>
-          <t>Dominga chaccara López mz i lote 11</t>
+          <t xml:space="preserve">MARIA NORABUENA ESPADA   Mz C Lt 36    N. recibo 16992      </t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 20:52:08</t>
+          <t>03/06/2026 18:24:18</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N50" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O50" s="19" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="20" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R50" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S50" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" s="21" t="n">
-        <v>2</v>
+      <c r="U50" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V50" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>U0405</t>
+          <t>U0499</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>FELIX LUNA LOPEZ</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>TITO COSME CASTILLEJO</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -4351,65 +4472,65 @@
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>Maria Alv*</t>
+          <t>Nancy Mon*</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr"/>
       <c r="H51" s="16" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="I51" s="16" t="inlineStr"/>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tito cosme castillejo Mz.H1.Lt.36</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 19:50:28</t>
+          <t>03/06/2026 16:20:52</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="18" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="N51" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O51" s="19" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R51" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S51" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr"/>
-      <c r="U51" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V51" s="31" t="n">
-        <v>2</v>
+      <c r="U51" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V51" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>U0066</t>
+          <t>U0222</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>MARIA NORABUENA ESPADA</t>
+          <t>AGUSTINA CALDAS CORZO</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4425,62 +4546,65 @@
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>BCP - JACOME NORABUENA JESUS ELVIRO</t>
+          <t>Hellen Val*</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr"/>
       <c r="H52" s="16" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I52" s="16" t="inlineStr"/>
       <c r="J52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA NORABUENA ESPADA   Mz C Lt 36    N. recibo 16992      </t>
+          <t>AGUSTINA CALDAS CORZO  MZ "L" LT "15"</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 18:24:18</t>
+          <t>03/06/2026 15:27:57</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N52" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O52" s="19" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
       <c r="Q52" s="20" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="R52" s="20" t="n">
-        <v>-125</v>
-      </c>
-      <c r="S52" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S52" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr"/>
-      <c r="U52" s="21" t="n">
-        <v>2</v>
+      <c r="U52" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V52" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>U0499</t>
+          <t>U0337</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>TITO COSME CASTILLEJO</t>
+          <t>RIVET VILLANUEVA ALEGRIA</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -4496,67 +4620,70 @@
       </c>
       <c r="F53" s="15" t="inlineStr">
         <is>
-          <t>Nancy Mon*</t>
+          <t>Rivet Vil*</t>
         </is>
       </c>
       <c r="G53" s="15" t="inlineStr"/>
       <c r="H53" s="16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I53" s="16" t="inlineStr"/>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>Tito cosme castillejo Mz.H1.Lt.36</t>
+          <t>mz T Lt 11</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 16:20:52</t>
+          <t>03/06/2026 11:05:43</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>T</t>
         </is>
       </c>
       <c r="N53" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O53" s="19" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R53" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S53" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr"/>
-      <c r="U53" s="21" t="n">
-        <v>2</v>
+      <c r="U53" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V53" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>U0222</t>
+          <t>U0178</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>AGUSTINA CALDAS CORZO</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>ADOLFO ROSARIO ROJAS</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>maestro</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -4567,67 +4694,66 @@
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Hellen Val*</t>
+          <t>Adolfo Ros*</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr"/>
       <c r="H54" s="16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I54" s="16" t="inlineStr"/>
       <c r="J54" s="17" t="inlineStr">
         <is>
-          <t>AGUSTINA CALDAS CORZO  MZ "L" LT "15"</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 15:27:57</t>
+          <t>02/06/2026 07:44:53</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="N54" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O54" s="19" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R54" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S54" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="21" t="n">
-        <v>2</v>
+      <c r="U54" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V54" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>U0337</t>
-        </is>
-      </c>
+      <c r="A55" s="12" t="inlineStr"/>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>RIVET VILLANUEVA ALEGRIA</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
+          <t>IGLESIA EVANGELICA BAUTISTA</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
+        <is>
+          <t>correccion</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -4638,67 +4764,70 @@
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>Rivet Vil*</t>
+          <t>Ramon Req*</t>
         </is>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
       <c r="H55" s="16" t="n">
-        <v>38</v>
+        <v>266</v>
       </c>
       <c r="I55" s="16" t="inlineStr"/>
       <c r="J55" s="17" t="inlineStr">
         <is>
-          <t>mz T Lt 11</t>
+          <t>del 2019 hasta octubre 2025</t>
         </is>
       </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
-          <t>03/06/2026 11:05:43</t>
+          <t>01/06/2026 18:34:12</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="18" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N55" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O55" s="19" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr"/>
       <c r="Q55" s="20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R55" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="14" t="inlineStr">
-        <is>
-          <t>exacto</t>
+      <c r="S55" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr"/>
-      <c r="U55" s="21" t="n">
-        <v>2</v>
+      <c r="U55" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V55" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>U0178</t>
+          <t>U0020</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>ADOLFO ROSARIO ROJAS</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>ROSALINA OLIMPIA CIRIACO SOTELO</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -4709,66 +4838,70 @@
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Adolfo Ros*</t>
+          <t>Rosalina Cir*</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr"/>
       <c r="H56" s="16" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I56" s="16" t="inlineStr"/>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mz.b Lt8 ROSALINA CIRIACO SOTELO</t>
         </is>
       </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026 07:44:53</t>
+          <t>30/05/2026 11:41:28</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N56" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O56" s="19" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
       <c r="Q56" s="20" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="R56" s="20" t="n">
-        <v>-118</v>
-      </c>
-      <c r="S56" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S56" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr"/>
-      <c r="U56" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V56" s="31" t="n">
-        <v>2</v>
+      <c r="U56" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V56" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="12" t="inlineStr"/>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>U0455</t>
+        </is>
+      </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>IGLESIA EVANGELICA BAUTISTA</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="inlineStr">
-        <is>
-          <t>correccion</t>
+          <t>EVER CERVANTES CHAVES</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>mensaje</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -4779,33 +4912,33 @@
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Ramon Req*</t>
+          <t>Ever Cer*</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr"/>
       <c r="H57" s="16" t="n">
-        <v>266</v>
+        <v>8</v>
       </c>
       <c r="I57" s="16" t="inlineStr"/>
       <c r="J57" s="17" t="inlineStr">
         <is>
-          <t>del 2019 hasta octubre 2025</t>
+          <t>MZ C1 LT 15</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
-          <t>01/06/2026 18:34:12</t>
+          <t>27/05/2026 07:00:40</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="N57" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O57" s="19" t="inlineStr"/>
@@ -4816,28 +4949,28 @@
       <c r="R57" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="26" t="inlineStr">
+      <c r="S57" s="21" t="inlineStr">
         <is>
           <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr"/>
-      <c r="U57" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V57" s="31" t="n">
-        <v>2</v>
+      <c r="U57" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V57" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>U0020</t>
+          <t>U0417</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>ROSALINA OLIMPIA CIRIACO SOTELO</t>
+          <t>ROSA DURAND SALES</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4853,62 +4986,65 @@
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Rosalina Cir*</t>
+          <t>Carolyn Mar*</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr"/>
       <c r="H58" s="16" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="I58" s="16" t="inlineStr"/>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>Mz.b Lt8 ROSALINA CIRIACO SOTELO</t>
+          <t>Mz Z Lt.14</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
-          <t>30/05/2026 11:41:28</t>
+          <t>22/05/2026 18:17:44</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="N58" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O58" s="19" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
       <c r="Q58" s="20" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R58" s="20" t="n">
-        <v>-98</v>
-      </c>
-      <c r="S58" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S58" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr"/>
-      <c r="U58" s="21" t="n">
-        <v>2</v>
+      <c r="U58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V58" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>U0455</t>
+          <t>U0229</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>EVER CERVANTES CHAVES</t>
+          <t>VICTORIA COCHACHIN CASIO</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
@@ -4924,193 +5060,54 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>Ever Cer*</t>
+          <t>Brilly Pan*</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr"/>
       <c r="H59" s="16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I59" s="16" t="inlineStr"/>
       <c r="J59" s="17" t="inlineStr">
         <is>
-          <t>MZ C1 LT 15</t>
+          <t>victoria cochachin   mz:M  lt:7</t>
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026 07:00:40</t>
+          <t>19/05/2026 19:14:27</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="18" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N59" s="18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O59" s="19" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
       <c r="Q59" s="20" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R59" s="20" t="n">
-        <v>-50</v>
-      </c>
-      <c r="S59" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
+        <v>0</v>
+      </c>
+      <c r="S59" s="21" t="inlineStr">
+        <is>
+          <t>sin deuda en planilla</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr"/>
-      <c r="U59" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>U0417</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
-        <is>
-          <t>ROSA DURAND SALES</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>TE PAGÓ</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>Carolyn Mar*</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr"/>
-      <c r="H60" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr"/>
-      <c r="J60" s="17" t="inlineStr">
-        <is>
-          <t>Mz Z Lt.14</t>
-        </is>
-      </c>
-      <c r="K60" s="15" t="inlineStr">
-        <is>
-          <t>22/05/2026 18:17:44</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="18" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="N60" s="18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O60" s="19" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
-      <c r="Q60" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="R60" s="20" t="n">
-        <v>-82</v>
-      </c>
-      <c r="S60" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr"/>
-      <c r="U60" s="21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>U0229</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>VICTORIA COCHACHIN CASIO</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>mensaje</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>TE PAGÓ</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr">
-        <is>
-          <t>Brilly Pan*</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr"/>
-      <c r="H61" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr"/>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>victoria cochachin   mz:M  lt:7</t>
-        </is>
-      </c>
-      <c r="K61" s="15" t="inlineStr">
-        <is>
-          <t>19/05/2026 19:14:27</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N61" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O61" s="19" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="R61" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="S61" s="25" t="inlineStr">
-        <is>
-          <t>parcial</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr"/>
-      <c r="U61" s="21" t="n">
-        <v>2</v>
+      <c r="U59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V59" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
